--- a/teacher_forms/004_school_administrator_evaluation_form--teacher_forms.xlsx
+++ b/teacher_forms/004_school_administrator_evaluation_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SchoolAdministrator</t>
+          <t>School Administrator Performance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Communication Skills</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Leadership Style</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SchoolAdministrator</t>
+          <t>School Administrator</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Communication 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,13 +686,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Leadership 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Evaluation Summary</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -711,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -757,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -774,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -791,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -808,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -825,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -842,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -859,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -876,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -893,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -910,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mr._smith'}</t>
+          <t>mr._smith</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mr. Smith'}</t>
+          <t>Mr. Smith</t>
         </is>
       </c>
     </row>
@@ -927,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mrs._doe'}</t>
+          <t>mrs._doe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mrs. Doe'}</t>
+          <t>Mrs. Doe</t>
         </is>
       </c>
     </row>
@@ -944,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -961,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -978,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -995,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
